--- a/fhir/ig/cl-urgencia/0.2.0/CodeSystem-medio-llegada.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/CodeSystem-medio-llegada.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/CodeSystem/medio-llegada</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/CodeSystem/medio-llegada</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:36:45-03:00</t>
+    <t>2026-09-24T11:47:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/ig/cl-urgencia/0.2.0/CodeSystem-medio-llegada.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/CodeSystem-medio-llegada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
